--- a/UnifacDortmund/Experimental_Data/data/profile_coeffs.xlsx
+++ b/UnifacDortmund/Experimental_Data/data/profile_coeffs.xlsx
@@ -1,20 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Juan\proyectos_personales\Maestría\Materias\Tesis\oleosim\UnifacDortmund\Experimental_Data\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8A0F0B-2D4C-4148-87CB-59A8A4787BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="21">
   <si>
     <t>Ref</t>
   </si>
@@ -60,16 +79,34 @@
   <si>
     <t>Yes</t>
   </si>
+  <si>
+    <t>Type Alcohol</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0;[Red]-#,##0"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000;[Red]-#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0;[Red]\-#,##0"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -109,44 +146,66 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0;[Red]-#,##0"/>
+      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
     </dxf>
-    <dxf/>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]-#,##0.000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="#,##0;[Red]\-#,##0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H126" totalsRowShown="0">
-  <autoFilter ref="A1:H126"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="Ref" dataDxfId="0"/>
-    <tableColumn id="2" name="Sub Ref" dataDxfId="1"/>
-    <tableColumn id="3" name="MAG/DAG Profile?" dataDxfId="1"/>
-    <tableColumn id="4" name="Additional FAME Profile?" dataDxfId="1"/>
-    <tableColumn id="5" name="Acid mix Profile?" dataDxfId="1"/>
-    <tableColumn id="6" name="m" dataDxfId="2"/>
-    <tableColumn id="7" name="n" dataDxfId="2"/>
-    <tableColumn id="8" name="p" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Frame0" displayName="Frame0" ref="A1:J138" totalsRowShown="0">
+  <autoFilter ref="A1:J138" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Ref" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Sub Ref"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="MAG/DAG Profile?"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Additional FAME Profile?"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Acid mix Profile?"/>
+    <tableColumn id="9" xr3:uid="{9F057E55-9F2C-4F9F-BF85-42F7D5BDEAEE}" name="Type Alcohol" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="m" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="n" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="p" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{A79D96DD-C468-4203-886B-C43662C6B702}" name="b" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -184,7 +243,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -218,6 +277,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -252,9 +312,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -427,11 +488,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H126"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J138"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -448,16 +509,22 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -473,17 +540,23 @@
       <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3">
         <v>12.99124001374472</v>
       </c>
-      <c r="G2" s="3">
-        <v>1.043695298325764</v>
-      </c>
       <c r="H2" s="3">
-        <v>0.9042156923016668</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>1.0436952983257639</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0.90421569230166676</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -499,17 +572,23 @@
       <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
+        <v>2</v>
+      </c>
+      <c r="G3" s="3">
         <v>12.88855175349229</v>
       </c>
-      <c r="G3" s="3">
-        <v>1.288995948379071</v>
-      </c>
       <c r="H3" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>1.2889959483790709</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -525,17 +604,23 @@
       <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="3">
-        <v>15.90023266097245</v>
+      <c r="F4" s="2">
+        <v>2</v>
       </c>
       <c r="G4" s="3">
+        <v>15.900232660972449</v>
+      </c>
+      <c r="H4" s="3">
         <v>1.145124362515882</v>
       </c>
-      <c r="H4" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -551,17 +636,23 @@
       <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3">
         <v>12.95188544251042</v>
       </c>
-      <c r="G5" s="3">
-        <v>1.455246309550437</v>
-      </c>
       <c r="H5" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>1.4552463095504371</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -577,17 +668,23 @@
       <c r="E6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="3">
-        <v>13.1790527244182</v>
+      <c r="F6" s="2">
+        <v>1</v>
       </c>
       <c r="G6" s="3">
+        <v>13.179052724418201</v>
+      </c>
+      <c r="H6" s="3">
         <v>1.357539365210557</v>
       </c>
-      <c r="H6" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -603,17 +700,23 @@
       <c r="E7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
+        <v>2</v>
+      </c>
+      <c r="G7" s="3">
         <v>12.74366639656704</v>
       </c>
-      <c r="G7" s="3">
-        <v>1.49144649215942</v>
-      </c>
       <c r="H7" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>1.4914464921594199</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -629,17 +732,23 @@
       <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3">
         <v>13.326537781866</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1.164598889148063</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -655,17 +764,23 @@
       <c r="E9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3">
         <v>12.70566613978518</v>
       </c>
-      <c r="G9" s="3">
-        <v>1.525733154335381</v>
-      </c>
       <c r="H9" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>1.5257331543353809</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -681,17 +796,23 @@
       <c r="E10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
+        <v>2</v>
+      </c>
+      <c r="G10" s="3">
         <v>12.65408035800184</v>
       </c>
-      <c r="G10" s="3">
-        <v>1.539450526251043</v>
-      </c>
       <c r="H10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>1.5394505262510429</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -707,17 +828,23 @@
       <c r="E11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="3">
-        <v>12.8592488724785</v>
+      <c r="F11" s="2">
+        <v>2</v>
       </c>
       <c r="G11" s="3">
-        <v>1.476728784589625</v>
+        <v>12.859248872478499</v>
       </c>
       <c r="H11" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>1.4767287845896251</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -733,17 +860,23 @@
       <c r="E12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="3">
-        <v>12.78992030308754</v>
+      <c r="F12" s="2">
+        <v>2</v>
       </c>
       <c r="G12" s="3">
-        <v>1.527717537784231</v>
+        <v>12.789920303087539</v>
       </c>
       <c r="H12" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>1.5277175377842309</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -759,17 +892,23 @@
       <c r="E13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
+        <v>2</v>
+      </c>
+      <c r="G13" s="3">
         <v>11.133217944441</v>
       </c>
-      <c r="G13" s="3">
-        <v>0.1872389182730338</v>
-      </c>
       <c r="H13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>0.18723891827303379</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -785,17 +924,23 @@
       <c r="E14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="3">
-        <v>12</v>
+      <c r="F14" s="2">
+        <v>2</v>
       </c>
       <c r="G14" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>2</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -811,17 +956,23 @@
       <c r="E15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
+        <v>2</v>
+      </c>
+      <c r="G15" s="3">
         <v>14</v>
       </c>
-      <c r="G15" s="3">
-        <v>1</v>
-      </c>
       <c r="H15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>1</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -837,17 +988,23 @@
       <c r="E16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
+        <v>2</v>
+      </c>
+      <c r="G16" s="3">
         <v>14</v>
       </c>
-      <c r="G16" s="3">
-        <v>0</v>
-      </c>
       <c r="H16" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" s="3">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>12</v>
       </c>
@@ -863,17 +1020,23 @@
       <c r="E17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
+        <v>2</v>
+      </c>
+      <c r="G17" s="3">
         <v>10</v>
       </c>
-      <c r="G17" s="3">
-        <v>0</v>
-      </c>
       <c r="H17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>13</v>
       </c>
@@ -889,17 +1052,23 @@
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
+        <v>2</v>
+      </c>
+      <c r="G18" s="3">
         <v>13.674442396701</v>
       </c>
-      <c r="G18" s="3">
-        <v>0.9064029551118191</v>
-      </c>
       <c r="H18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <v>0.90640295511181912</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>14</v>
       </c>
@@ -915,17 +1084,23 @@
       <c r="E19" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3">
         <v>13.17208607940198</v>
       </c>
-      <c r="G19" s="3">
+      <c r="H19" s="3">
         <v>1.279842208804453</v>
       </c>
-      <c r="H19" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19" s="3">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>15</v>
       </c>
@@ -941,17 +1116,23 @@
       <c r="E20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="3">
-        <v>13.28859559632168</v>
+      <c r="F20" s="2">
+        <v>1</v>
       </c>
       <c r="G20" s="3">
-        <v>1.303043957499863</v>
+        <v>13.288595596321681</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+        <v>1.3030439574998629</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>16</v>
       </c>
@@ -967,17 +1148,23 @@
       <c r="E21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="2">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3">
         <v>14</v>
       </c>
-      <c r="G21" s="3">
-        <v>1</v>
-      </c>
       <c r="H21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+        <v>1</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>17</v>
       </c>
@@ -993,17 +1180,23 @@
       <c r="E22" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="3">
-        <v>13.02541682896731</v>
+      <c r="F22" s="2">
+        <v>1</v>
       </c>
       <c r="G22" s="3">
-        <v>1.014068726355177</v>
+        <v>13.025416828967311</v>
       </c>
       <c r="H22" s="3">
+        <v>1.0140687263551771</v>
+      </c>
+      <c r="I22" s="3">
         <v>0.9149194700052542</v>
       </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="J22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>18</v>
       </c>
@@ -1019,17 +1212,23 @@
       <c r="E23" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="2">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3">
         <v>12.75843701270664</v>
       </c>
-      <c r="G23" s="3">
-        <v>1.51103026078724</v>
-      </c>
       <c r="H23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+        <v>1.5110302607872399</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>19</v>
       </c>
@@ -1045,17 +1244,23 @@
       <c r="E24" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="2">
+        <v>1</v>
+      </c>
+      <c r="G24" s="3">
         <v>12.99837355647462</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1.364014236928502</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>19</v>
       </c>
@@ -1071,17 +1276,23 @@
       <c r="E25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="2">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3">
         <v>13.39820426215049</v>
       </c>
-      <c r="G25" s="3">
-        <v>1.032032936637875</v>
-      </c>
       <c r="H25" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>1.0320329366378751</v>
+      </c>
+      <c r="I25" s="3">
+        <v>0</v>
+      </c>
+      <c r="J25" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>20</v>
       </c>
@@ -1097,17 +1308,23 @@
       <c r="E26" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="2">
+        <v>2</v>
+      </c>
+      <c r="G26" s="3">
         <v>13.85138576450859</v>
       </c>
-      <c r="G26" s="3">
-        <v>0.5877971166334097</v>
-      </c>
       <c r="H26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+        <v>0.58779711663340972</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>21</v>
       </c>
@@ -1123,17 +1340,23 @@
       <c r="E27" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="2">
+        <v>2</v>
+      </c>
+      <c r="G27" s="3">
         <v>13.13351771380986</v>
       </c>
-      <c r="G27" s="3">
-        <v>1.306481428636736</v>
-      </c>
       <c r="H27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>1.3064814286367361</v>
+      </c>
+      <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>22</v>
       </c>
@@ -1149,17 +1372,23 @@
       <c r="E28" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F28" s="3">
-        <v>13.14115247751626</v>
+      <c r="F28" s="2">
+        <v>2</v>
       </c>
       <c r="G28" s="3">
-        <v>1.251195608807394</v>
+        <v>13.141152477516259</v>
       </c>
       <c r="H28" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>1.2511956088073941</v>
+      </c>
+      <c r="I28" s="3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>23</v>
       </c>
@@ -1175,17 +1404,23 @@
       <c r="E29" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="2">
+        <v>2</v>
+      </c>
+      <c r="G29" s="3">
         <v>17.05411199780443</v>
       </c>
-      <c r="G29" s="3">
-        <v>0.5980202956098233</v>
-      </c>
       <c r="H29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>0.59802029560982328</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>23</v>
       </c>
@@ -1201,17 +1436,23 @@
       <c r="E30" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F30" s="3">
-        <v>14.09269499660265</v>
+      <c r="F30" s="2">
+        <v>2</v>
       </c>
       <c r="G30" s="3">
+        <v>14.092694996602649</v>
+      </c>
+      <c r="H30" s="3">
         <v>1.223277357224446</v>
       </c>
-      <c r="H30" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+      <c r="I30" s="3">
+        <v>0</v>
+      </c>
+      <c r="J30" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>23</v>
       </c>
@@ -1227,17 +1468,23 @@
       <c r="E31" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="3">
-        <v>13.72884127477984</v>
+      <c r="F31" s="2">
+        <v>2</v>
       </c>
       <c r="G31" s="3">
-        <v>0.8668336220841426</v>
+        <v>13.728841274779841</v>
       </c>
       <c r="H31" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
+        <v>0.86683362208414261</v>
+      </c>
+      <c r="I31" s="3">
+        <v>0</v>
+      </c>
+      <c r="J31" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24</v>
       </c>
@@ -1253,17 +1500,23 @@
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="2">
+        <v>1</v>
+      </c>
+      <c r="G32" s="3">
         <v>13.3610523378059</v>
       </c>
-      <c r="G32" s="3">
-        <v>1.0852390346741</v>
-      </c>
       <c r="H32" s="3">
-        <v>0.05418261263977318</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
+        <v>1.0852390346741001</v>
+      </c>
+      <c r="I32" s="3">
+        <v>5.4182612639773177E-2</v>
+      </c>
+      <c r="J32" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>25</v>
       </c>
@@ -1279,17 +1532,23 @@
       <c r="E33" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F33" s="3">
-        <v>13.56853899379385</v>
+      <c r="F33" s="2">
+        <v>1</v>
       </c>
       <c r="G33" s="3">
+        <v>13.568538993793849</v>
+      </c>
+      <c r="H33" s="3">
         <v>1.043776501423834</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+      <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>26</v>
       </c>
@@ -1305,17 +1564,23 @@
       <c r="E34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="2">
+        <v>1</v>
+      </c>
+      <c r="G34" s="3">
         <v>13.51753666100233</v>
       </c>
-      <c r="G34" s="3">
-        <v>1.194287278439318</v>
-      </c>
       <c r="H34" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>1.1942872784393179</v>
+      </c>
+      <c r="I34" s="3">
+        <v>0</v>
+      </c>
+      <c r="J34" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>26</v>
       </c>
@@ -1331,17 +1596,23 @@
       <c r="E35" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="2">
+        <v>1</v>
+      </c>
+      <c r="G35" s="3">
         <v>12.94804860701996</v>
       </c>
-      <c r="G35" s="3">
-        <v>1.384579555987454</v>
-      </c>
       <c r="H35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+        <v>1.3845795559874541</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>27</v>
       </c>
@@ -1357,100 +1628,124 @@
       <c r="E36" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F36" s="3">
-        <v>13.01997867427088</v>
+      <c r="F36" s="2">
+        <v>1</v>
       </c>
       <c r="G36" s="3">
-        <v>1.032557376825444</v>
+        <v>13.019978674270879</v>
       </c>
       <c r="H36" s="3">
-        <v>0.8821149176814088</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+        <v>1.0325573768254439</v>
+      </c>
+      <c r="I36" s="3">
+        <v>0.88211491768140882</v>
+      </c>
+      <c r="J36" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
+        <v>27</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="2">
+        <v>2</v>
+      </c>
+      <c r="G37" s="3">
+        <v>13.019978674270879</v>
+      </c>
+      <c r="H37" s="3">
+        <v>1.0325573768254439</v>
+      </c>
+      <c r="I37" s="3">
+        <v>0.88211491768140882</v>
+      </c>
+      <c r="J37" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>27</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="2">
+        <v>4</v>
+      </c>
+      <c r="G38" s="3">
+        <v>13.019978674270879</v>
+      </c>
+      <c r="H38" s="3">
+        <v>1.0325573768254439</v>
+      </c>
+      <c r="I38" s="3">
+        <v>0.88211491768140882</v>
+      </c>
+      <c r="J38" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
         <v>28</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" s="3">
+      <c r="B39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="2">
+        <v>2</v>
+      </c>
+      <c r="G39" s="3">
         <v>12.81307324391433</v>
       </c>
-      <c r="G37" s="3">
-        <v>1.461858135014705</v>
-      </c>
-      <c r="H37" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="1">
-        <v>29</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" s="3">
-        <v>14</v>
-      </c>
-      <c r="G38" s="3">
-        <v>1</v>
-      </c>
-      <c r="H38" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="1">
-        <v>29</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F39" s="3">
-        <v>13.78252973372312</v>
-      </c>
-      <c r="G39" s="3">
-        <v>0.9850603720590058</v>
-      </c>
       <c r="H39" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+        <v>1.4618581350147051</v>
+      </c>
+      <c r="I39" s="3">
+        <v>0</v>
+      </c>
+      <c r="J39" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>29</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>12</v>
@@ -1461,22 +1756,28 @@
       <c r="E40" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F40" s="3">
-        <v>13.06811299163466</v>
+      <c r="F40" s="2">
+        <v>2</v>
       </c>
       <c r="G40" s="3">
-        <v>1.343247991934211</v>
+        <v>14</v>
       </c>
       <c r="H40" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+        <v>1</v>
+      </c>
+      <c r="I40" s="3">
+        <v>0</v>
+      </c>
+      <c r="J40" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>29</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>12</v>
@@ -1487,22 +1788,28 @@
       <c r="E41" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="2">
+        <v>2</v>
+      </c>
+      <c r="G41" s="3">
         <v>13.78252973372312</v>
       </c>
-      <c r="G41" s="3">
-        <v>0.9850603720590058</v>
-      </c>
       <c r="H41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
+        <v>0.98506037205900576</v>
+      </c>
+      <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>12</v>
@@ -1513,22 +1820,28 @@
       <c r="E42" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F42" s="3">
-        <v>12.83699106927911</v>
+      <c r="F42" s="2">
+        <v>2</v>
       </c>
       <c r="G42" s="3">
-        <v>1.414378586208382</v>
+        <v>13.06811299163466</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+        <v>1.3432479919342111</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>12</v>
@@ -1539,22 +1852,28 @@
       <c r="E43" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F43" s="3">
-        <v>12.60818319052277</v>
+      <c r="F43" s="2">
+        <v>2</v>
       </c>
       <c r="G43" s="3">
-        <v>1.623639561950906</v>
+        <v>13.78252973372312</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+        <v>0.98506037205900576</v>
+      </c>
+      <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>30</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>12</v>
@@ -1565,22 +1884,28 @@
       <c r="E44" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F44" s="3">
-        <v>12.91991368363948</v>
+      <c r="F44" s="2">
+        <v>2</v>
       </c>
       <c r="G44" s="3">
-        <v>1.276528599295026</v>
+        <v>12.83699106927911</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+        <v>1.414378586208382</v>
+      </c>
+      <c r="I44" s="3">
+        <v>0</v>
+      </c>
+      <c r="J44" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>30</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>12</v>
@@ -1591,22 +1916,28 @@
       <c r="E45" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F45" s="3">
-        <v>12.60818319052277</v>
+      <c r="F45" s="2">
+        <v>2</v>
       </c>
       <c r="G45" s="3">
-        <v>1.623639561950906</v>
+        <v>12.608183190522769</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
+        <v>1.6236395619509061</v>
+      </c>
+      <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>12</v>
@@ -1617,22 +1948,28 @@
       <c r="E46" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F46" s="3">
-        <v>13.25398333815373</v>
+      <c r="F46" s="2">
+        <v>2</v>
       </c>
       <c r="G46" s="3">
-        <v>1.166009014949074</v>
+        <v>12.91991368363948</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+        <v>1.2765285992950259</v>
+      </c>
+      <c r="I46" s="3">
+        <v>0</v>
+      </c>
+      <c r="J46" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>12</v>
@@ -1643,19 +1980,25 @@
       <c r="E47" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F47" s="3">
-        <v>13.82142218187953</v>
+      <c r="F47" s="2">
+        <v>2</v>
       </c>
       <c r="G47" s="3">
-        <v>1.031666044872852</v>
+        <v>12.608183190522769</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
+        <v>1.6236395619509061</v>
+      </c>
+      <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>8</v>
@@ -1669,19 +2012,25 @@
       <c r="E48" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F48" s="3">
-        <v>13.28234336837105</v>
+      <c r="F48" s="2">
+        <v>2</v>
       </c>
       <c r="G48" s="3">
-        <v>1.135003564437693</v>
+        <v>13.253983338153731</v>
       </c>
       <c r="H48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+        <v>1.1660090149490741</v>
+      </c>
+      <c r="I48" s="3">
+        <v>0</v>
+      </c>
+      <c r="J48" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>8</v>
@@ -1695,45 +2044,57 @@
       <c r="E49" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49" s="2">
+        <v>2</v>
+      </c>
+      <c r="G49" s="3">
+        <v>13.82142218187953</v>
+      </c>
+      <c r="H49" s="3">
+        <v>1.0316660448728521</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>32</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="2">
+        <v>2</v>
+      </c>
+      <c r="G50" s="3">
         <v>13.28234336837105</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H50" s="3">
         <v>1.135003564437693</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="1">
-        <v>33</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" s="3">
-        <v>13.06811299163466</v>
-      </c>
-      <c r="G50" s="3">
-        <v>1.343247991934211</v>
-      </c>
-      <c r="H50" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="I50" s="3">
+        <v>0</v>
+      </c>
+      <c r="J50" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>8</v>
@@ -1747,25 +2108,31 @@
       <c r="E51" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F51" s="3">
-        <v>13.80015421942349</v>
+      <c r="F51" s="2">
+        <v>2</v>
       </c>
       <c r="G51" s="3">
-        <v>1.006418085014643</v>
+        <v>13.28234336837105</v>
       </c>
       <c r="H51" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+        <v>1.135003564437693</v>
+      </c>
+      <c r="I51" s="3">
+        <v>0</v>
+      </c>
+      <c r="J51" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>12</v>
@@ -1773,19 +2140,25 @@
       <c r="E52" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F52" s="3">
-        <v>13.88221094135045</v>
+      <c r="F52" s="2">
+        <v>2</v>
       </c>
       <c r="G52" s="3">
-        <v>0.5735849903613897</v>
+        <v>13.06811299163466</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+        <v>1.3432479919342111</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>8</v>
@@ -1799,25 +2172,31 @@
       <c r="E53" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F53" s="3">
-        <v>13.95748809512908</v>
+      <c r="F53" s="2">
+        <v>2</v>
       </c>
       <c r="G53" s="3">
-        <v>0</v>
+        <v>13.80015421942349</v>
       </c>
       <c r="H53" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
+        <v>1.0064180850146429</v>
+      </c>
+      <c r="I53" s="3">
+        <v>0</v>
+      </c>
+      <c r="J53" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>34</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>12</v>
@@ -1825,22 +2204,28 @@
       <c r="E54" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F54" s="3">
-        <v>13.88221094135045</v>
+      <c r="F54" s="2">
+        <v>2</v>
       </c>
       <c r="G54" s="3">
-        <v>0.5735849903613897</v>
+        <v>13.882210941350451</v>
       </c>
       <c r="H54" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
+        <v>0.57358499036138966</v>
+      </c>
+      <c r="I54" s="3">
+        <v>0</v>
+      </c>
+      <c r="J54" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>34</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>12</v>
@@ -1851,22 +2236,28 @@
       <c r="E55" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F55" s="3">
-        <v>13.7204976822732</v>
+      <c r="F55" s="2">
+        <v>2</v>
       </c>
       <c r="G55" s="3">
-        <v>1.031800633199491</v>
+        <v>13.957488095129079</v>
       </c>
       <c r="H55" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:8">
+      <c r="I55" s="3">
+        <v>0</v>
+      </c>
+      <c r="J55" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>12</v>
@@ -1877,22 +2268,28 @@
       <c r="E56" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F56" s="3">
-        <v>13.07296932663911</v>
+      <c r="F56" s="2">
+        <v>2</v>
       </c>
       <c r="G56" s="3">
-        <v>1.402501186016084</v>
+        <v>13.882210941350451</v>
       </c>
       <c r="H56" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+        <v>0.57358499036138966</v>
+      </c>
+      <c r="I56" s="3">
+        <v>0</v>
+      </c>
+      <c r="J56" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>12</v>
@@ -1903,19 +2300,25 @@
       <c r="E57" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F57" s="3">
-        <v>13.78593994877482</v>
+      <c r="F57" s="2">
+        <v>2</v>
       </c>
       <c r="G57" s="3">
-        <v>0.9695716254129194</v>
+        <v>13.7204976822732</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
+        <v>1.0318006331994909</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>8</v>
@@ -1929,19 +2332,25 @@
       <c r="E58" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F58" s="3">
-        <v>12.11252482206938</v>
+      <c r="F58" s="2">
+        <v>1</v>
       </c>
       <c r="G58" s="3">
-        <v>0.6437517503145203</v>
+        <v>13.072969326639109</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
+        <v>1.4025011860160841</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>8</v>
@@ -1955,22 +2364,28 @@
       <c r="E59" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F59" s="3">
-        <v>14</v>
+      <c r="F59" s="2">
+        <v>1</v>
       </c>
       <c r="G59" s="3">
-        <v>1</v>
+        <v>13.78593994877482</v>
       </c>
       <c r="H59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+        <v>0.96957162541291941</v>
+      </c>
+      <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>12</v>
@@ -1981,22 +2396,28 @@
       <c r="E60" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F60" s="3">
-        <v>13.07741484374226</v>
+      <c r="F60" s="2">
+        <v>2</v>
       </c>
       <c r="G60" s="3">
-        <v>1.326260757365857</v>
+        <v>13.072969326639109</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+        <v>1.4025011860160841</v>
+      </c>
+      <c r="I60" s="3">
+        <v>0</v>
+      </c>
+      <c r="J60" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>12</v>
@@ -2007,22 +2428,28 @@
       <c r="E61" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F61" s="3">
-        <v>12</v>
+      <c r="F61" s="2">
+        <v>2</v>
       </c>
       <c r="G61" s="3">
-        <v>2</v>
+        <v>13.78593994877482</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+        <v>0.96957162541291941</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>12</v>
@@ -2033,22 +2460,28 @@
       <c r="E62" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F62" s="3">
-        <v>12.7732305275222</v>
+      <c r="F62" s="2">
+        <v>3</v>
       </c>
       <c r="G62" s="3">
-        <v>1.547997760991404</v>
+        <v>13.072969326639109</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
+        <v>1.4025011860160841</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>12</v>
@@ -2059,22 +2492,28 @@
       <c r="E63" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F63" s="3">
-        <v>12.60818319052277</v>
+      <c r="F63" s="2">
+        <v>3</v>
       </c>
       <c r="G63" s="3">
-        <v>1.623639561950906</v>
+        <v>13.78593994877482</v>
       </c>
       <c r="H63" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
+        <v>0.96957162541291941</v>
+      </c>
+      <c r="I63" s="3">
+        <v>0</v>
+      </c>
+      <c r="J63" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>12</v>
@@ -2085,22 +2524,28 @@
       <c r="E64" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F64" s="3">
-        <v>12.86475715871716</v>
+      <c r="F64" s="2">
+        <v>2</v>
       </c>
       <c r="G64" s="3">
-        <v>1.453941730161083</v>
+        <v>12.11252482206938</v>
       </c>
       <c r="H64" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
+        <v>0.64375175031452025</v>
+      </c>
+      <c r="I64" s="3">
+        <v>0</v>
+      </c>
+      <c r="J64" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>12</v>
@@ -2111,19 +2556,25 @@
       <c r="E65" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F65" s="3">
-        <v>12.60818319052277</v>
+      <c r="F65" s="2">
+        <v>2</v>
       </c>
       <c r="G65" s="3">
-        <v>1.623639561950906</v>
+        <v>14</v>
       </c>
       <c r="H65" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
+        <v>1</v>
+      </c>
+      <c r="I65" s="3">
+        <v>0</v>
+      </c>
+      <c r="J65" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>8</v>
@@ -2137,19 +2588,25 @@
       <c r="E66" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F66" s="3">
-        <v>12.83463677292898</v>
+      <c r="F66" s="2">
+        <v>2</v>
       </c>
       <c r="G66" s="3">
-        <v>1.472305361134222</v>
+        <v>13.077414843742259</v>
       </c>
       <c r="H66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
+        <v>1.3262607573658569</v>
+      </c>
+      <c r="I66" s="3">
+        <v>0</v>
+      </c>
+      <c r="J66" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>8</v>
@@ -2163,22 +2620,28 @@
       <c r="E67" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F67" s="3">
-        <v>12.66202168764096</v>
+      <c r="F67" s="2">
+        <v>2</v>
       </c>
       <c r="G67" s="3">
-        <v>1.585977455906777</v>
+        <v>12</v>
       </c>
       <c r="H67" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
+        <v>2</v>
+      </c>
+      <c r="I67" s="3">
+        <v>0</v>
+      </c>
+      <c r="J67" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>12</v>
@@ -2189,22 +2652,28 @@
       <c r="E68" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F68" s="3">
-        <v>12.71466686734469</v>
+      <c r="F68" s="2">
+        <v>2</v>
       </c>
       <c r="G68" s="3">
-        <v>1.192958522944296</v>
+        <v>12.7732305275222</v>
       </c>
       <c r="H68" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
+        <v>1.547997760991404</v>
+      </c>
+      <c r="I68" s="3">
+        <v>0</v>
+      </c>
+      <c r="J68" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>12</v>
@@ -2215,22 +2684,28 @@
       <c r="E69" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F69" s="3">
-        <v>13.70405998839362</v>
+      <c r="F69" s="2">
+        <v>2</v>
       </c>
       <c r="G69" s="3">
-        <v>1.024976510202978</v>
+        <v>12.608183190522769</v>
       </c>
       <c r="H69" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
+        <v>1.6236395619509061</v>
+      </c>
+      <c r="I69" s="3">
+        <v>0</v>
+      </c>
+      <c r="J69" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>12</v>
@@ -2241,22 +2716,28 @@
       <c r="E70" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F70" s="3">
-        <v>13.20853656487486</v>
+      <c r="F70" s="2">
+        <v>2</v>
       </c>
       <c r="G70" s="3">
-        <v>1.171785098475806</v>
+        <v>12.864757158717159</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
+        <v>1.4539417301610831</v>
+      </c>
+      <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>12</v>
@@ -2267,19 +2748,25 @@
       <c r="E71" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F71" s="3">
-        <v>13.70405998839362</v>
+      <c r="F71" s="2">
+        <v>2</v>
       </c>
       <c r="G71" s="3">
-        <v>1.024976510202978</v>
+        <v>12.608183190522769</v>
       </c>
       <c r="H71" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8">
+        <v>1.6236395619509061</v>
+      </c>
+      <c r="I71" s="3">
+        <v>0</v>
+      </c>
+      <c r="J71" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>8</v>
@@ -2293,19 +2780,25 @@
       <c r="E72" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F72" s="3">
-        <v>12.71371920761699</v>
+      <c r="F72" s="2">
+        <v>2</v>
       </c>
       <c r="G72" s="3">
-        <v>1.567489090848544</v>
+        <v>12.834636772928979</v>
       </c>
       <c r="H72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
+        <v>1.4723053611342221</v>
+      </c>
+      <c r="I72" s="3">
+        <v>0</v>
+      </c>
+      <c r="J72" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>8</v>
@@ -2319,19 +2812,25 @@
       <c r="E73" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F73" s="3">
-        <v>13.79971211873246</v>
+      <c r="F73" s="2">
+        <v>2</v>
       </c>
       <c r="G73" s="3">
-        <v>1.006416508794234</v>
+        <v>12.66202168764096</v>
       </c>
       <c r="H73" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
+        <v>1.585977455906777</v>
+      </c>
+      <c r="I73" s="3">
+        <v>0</v>
+      </c>
+      <c r="J73" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>8</v>
@@ -2345,19 +2844,25 @@
       <c r="E74" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F74" s="3">
-        <v>12.78515953650012</v>
+      <c r="F74" s="2">
+        <v>2</v>
       </c>
       <c r="G74" s="3">
-        <v>1.485471931736494</v>
+        <v>12.71466686734469</v>
       </c>
       <c r="H74" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
+        <v>1.1929585229442961</v>
+      </c>
+      <c r="I74" s="3">
+        <v>0</v>
+      </c>
+      <c r="J74" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>8</v>
@@ -2371,22 +2876,28 @@
       <c r="E75" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F75" s="3">
-        <v>13.79971211873246</v>
+      <c r="F75" s="2">
+        <v>2</v>
       </c>
       <c r="G75" s="3">
-        <v>1.006416508794234</v>
+        <v>13.70405998839362</v>
       </c>
       <c r="H75" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
+        <v>1.024976510202978</v>
+      </c>
+      <c r="I75" s="3">
+        <v>0</v>
+      </c>
+      <c r="J75" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>12</v>
@@ -2397,22 +2908,28 @@
       <c r="E76" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F76" s="3">
-        <v>13.38796602306693</v>
+      <c r="F76" s="2">
+        <v>2</v>
       </c>
       <c r="G76" s="3">
-        <v>1.134440891232789</v>
+        <v>13.20853656487486</v>
       </c>
       <c r="H76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8">
+        <v>1.171785098475806</v>
+      </c>
+      <c r="I76" s="3">
+        <v>0</v>
+      </c>
+      <c r="J76" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>12</v>
@@ -2423,22 +2940,28 @@
       <c r="E77" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F77" s="3">
-        <v>12.66202168764096</v>
+      <c r="F77" s="2">
+        <v>2</v>
       </c>
       <c r="G77" s="3">
-        <v>1.585977455906777</v>
+        <v>13.70405998839362</v>
       </c>
       <c r="H77" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
+        <v>1.024976510202978</v>
+      </c>
+      <c r="I77" s="3">
+        <v>0</v>
+      </c>
+      <c r="J77" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>12</v>
@@ -2449,22 +2972,28 @@
       <c r="E78" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F78" s="3">
-        <v>13.8213879236479</v>
+      <c r="F78" s="2">
+        <v>2</v>
       </c>
       <c r="G78" s="3">
-        <v>0.8460053666973062</v>
+        <v>12.71371920761699</v>
       </c>
       <c r="H78" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8">
+        <v>1.5674890908485439</v>
+      </c>
+      <c r="I78" s="3">
+        <v>0</v>
+      </c>
+      <c r="J78" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>12</v>
@@ -2475,19 +3004,25 @@
       <c r="E79" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F79" s="3">
-        <v>12.66202168764096</v>
+      <c r="F79" s="2">
+        <v>2</v>
       </c>
       <c r="G79" s="3">
-        <v>1.585977455906777</v>
+        <v>13.79971211873246</v>
       </c>
       <c r="H79" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8">
+        <v>1.0064165087942341</v>
+      </c>
+      <c r="I79" s="3">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>8</v>
@@ -2501,19 +3036,25 @@
       <c r="E80" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F80" s="3">
-        <v>12.87597603066572</v>
+      <c r="F80" s="2">
+        <v>2</v>
       </c>
       <c r="G80" s="3">
-        <v>1.459152709879776</v>
+        <v>12.785159536500119</v>
       </c>
       <c r="H80" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8">
+        <v>1.4854719317364939</v>
+      </c>
+      <c r="I80" s="3">
+        <v>0</v>
+      </c>
+      <c r="J80" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>8</v>
@@ -2527,19 +3068,25 @@
       <c r="E81" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F81" s="3">
+      <c r="F81" s="2">
+        <v>2</v>
+      </c>
+      <c r="G81" s="3">
         <v>13.79971211873246</v>
       </c>
-      <c r="G81" s="3">
-        <v>1.006416508794234</v>
-      </c>
       <c r="H81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
+        <v>1.0064165087942341</v>
+      </c>
+      <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>8</v>
@@ -2553,19 +3100,25 @@
       <c r="E82" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F82" s="3">
-        <v>12.60700339919045</v>
+      <c r="F82" s="2">
+        <v>2</v>
       </c>
       <c r="G82" s="3">
-        <v>1.626488758689467</v>
+        <v>13.38796602306693</v>
       </c>
       <c r="H82" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
+        <v>1.134440891232789</v>
+      </c>
+      <c r="I82" s="3">
+        <v>0</v>
+      </c>
+      <c r="J82" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>8</v>
@@ -2579,19 +3132,25 @@
       <c r="E83" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F83" s="3">
-        <v>13.5758796301193</v>
+      <c r="F83" s="2">
+        <v>2</v>
       </c>
       <c r="G83" s="3">
-        <v>0.9972099111545972</v>
+        <v>12.66202168764096</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
+        <v>1.585977455906777</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>9</v>
@@ -2605,19 +3164,25 @@
       <c r="E84" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F84" s="3">
-        <v>12.88654148039067</v>
+      <c r="F84" s="2">
+        <v>2</v>
       </c>
       <c r="G84" s="3">
-        <v>1.488058263269652</v>
+        <v>13.821387923647899</v>
       </c>
       <c r="H84" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
+        <v>0.84600536669730619</v>
+      </c>
+      <c r="I84" s="3">
+        <v>0</v>
+      </c>
+      <c r="J84" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>9</v>
@@ -2631,19 +3196,25 @@
       <c r="E85" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F85" s="3">
-        <v>13.5758796301193</v>
+      <c r="F85" s="2">
+        <v>2</v>
       </c>
       <c r="G85" s="3">
-        <v>0.9972099111545972</v>
+        <v>12.66202168764096</v>
       </c>
       <c r="H85" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
+        <v>1.585977455906777</v>
+      </c>
+      <c r="I85" s="3">
+        <v>0</v>
+      </c>
+      <c r="J85" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>8</v>
@@ -2657,19 +3228,25 @@
       <c r="E86" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F86" s="3">
-        <v>12.80096282118333</v>
+      <c r="F86" s="2">
+        <v>2</v>
       </c>
       <c r="G86" s="3">
-        <v>1.477512303147689</v>
+        <v>12.87597603066572</v>
       </c>
       <c r="H86" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
+        <v>1.4591527098797761</v>
+      </c>
+      <c r="I86" s="3">
+        <v>0</v>
+      </c>
+      <c r="J86" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>8</v>
@@ -2683,19 +3260,25 @@
       <c r="E87" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F87" s="3">
+      <c r="F87" s="2">
+        <v>2</v>
+      </c>
+      <c r="G87" s="3">
         <v>13.79971211873246</v>
       </c>
-      <c r="G87" s="3">
-        <v>1.006416508794234</v>
-      </c>
       <c r="H87" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
+        <v>1.0064165087942341</v>
+      </c>
+      <c r="I87" s="3">
+        <v>0</v>
+      </c>
+      <c r="J87" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>8</v>
@@ -2709,19 +3292,25 @@
       <c r="E88" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F88" s="3">
-        <v>10.20580781269364</v>
+      <c r="F88" s="2">
+        <v>2</v>
       </c>
       <c r="G88" s="3">
-        <v>0.04627588256508246</v>
+        <v>12.60700339919045</v>
       </c>
       <c r="H88" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
+        <v>1.626488758689467</v>
+      </c>
+      <c r="I88" s="3">
+        <v>0</v>
+      </c>
+      <c r="J88" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>8</v>
@@ -2735,22 +3324,28 @@
       <c r="E89" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F89" s="3">
-        <v>10</v>
+      <c r="F89" s="2">
+        <v>2</v>
       </c>
       <c r="G89" s="3">
-        <v>0</v>
+        <v>13.575879630119299</v>
       </c>
       <c r="H89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8">
+        <v>0.99720991115459723</v>
+      </c>
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>12</v>
@@ -2761,19 +3356,25 @@
       <c r="E90" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F90" s="3">
-        <v>14.71692398648515</v>
+      <c r="F90" s="2">
+        <v>2</v>
       </c>
       <c r="G90" s="3">
-        <v>0.1653481874792032</v>
+        <v>12.886541480390671</v>
       </c>
       <c r="H90" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8">
+        <v>1.488058263269652</v>
+      </c>
+      <c r="I90" s="3">
+        <v>0</v>
+      </c>
+      <c r="J90" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>9</v>
@@ -2785,926 +3386,1526 @@
         <v>12</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F91" s="3">
-        <v>14.89677303113448</v>
+        <v>14</v>
+      </c>
+      <c r="F91" s="2">
+        <v>2</v>
       </c>
       <c r="G91" s="3">
-        <v>0.1875019478148285</v>
+        <v>13.575879630119299</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8">
+        <v>0.99720991115459723</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
+        <v>45</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F92" s="2">
+        <v>2</v>
+      </c>
+      <c r="G92" s="3">
+        <v>12.80096282118333</v>
+      </c>
+      <c r="H92" s="3">
+        <v>1.4775123031476891</v>
+      </c>
+      <c r="I92" s="3">
+        <v>0</v>
+      </c>
+      <c r="J92" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>45</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F93" s="2">
+        <v>2</v>
+      </c>
+      <c r="G93" s="3">
+        <v>13.79971211873246</v>
+      </c>
+      <c r="H93" s="3">
+        <v>1.0064165087942341</v>
+      </c>
+      <c r="I93" s="3">
+        <v>0</v>
+      </c>
+      <c r="J93" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>46</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F94" s="2">
+        <v>1</v>
+      </c>
+      <c r="G94" s="3">
+        <v>10.20580781269364</v>
+      </c>
+      <c r="H94" s="3">
+        <v>4.6275882565082457E-2</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>46</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F95" s="2">
+        <v>1</v>
+      </c>
+      <c r="G95" s="3">
+        <v>10</v>
+      </c>
+      <c r="H95" s="3">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3">
+        <v>0</v>
+      </c>
+      <c r="J95" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
         <v>47</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B96" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F96" s="2">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>14.716923986485151</v>
+      </c>
+      <c r="H96" s="3">
+        <v>0.16534818747920321</v>
+      </c>
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>47</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F97" s="2">
+        <v>0</v>
+      </c>
+      <c r="G97" s="3">
+        <v>14.896773031134479</v>
+      </c>
+      <c r="H97" s="3">
+        <v>0.18750194781482851</v>
+      </c>
+      <c r="I97" s="3">
+        <v>0</v>
+      </c>
+      <c r="J97" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>47</v>
+      </c>
+      <c r="B98" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F92" s="3">
+      <c r="C98" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F98" s="2">
+        <v>0</v>
+      </c>
+      <c r="G98" s="3">
         <v>14.55039495657187</v>
       </c>
-      <c r="G92" s="3">
-        <v>0.1527856539884437</v>
-      </c>
-      <c r="H92" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8">
-      <c r="A93" s="1">
+      <c r="H98" s="3">
+        <v>0.15278565398844371</v>
+      </c>
+      <c r="I98" s="3">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>47</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F99" s="2">
+        <v>1</v>
+      </c>
+      <c r="G99" s="3">
+        <v>14.716923986485151</v>
+      </c>
+      <c r="H99" s="3">
+        <v>0.16534818747920321</v>
+      </c>
+      <c r="I99" s="3">
+        <v>0</v>
+      </c>
+      <c r="J99" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>47</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F100" s="2">
+        <v>1</v>
+      </c>
+      <c r="G100" s="3">
+        <v>14.896773031134479</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0.18750194781482851</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>47</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F101" s="2">
+        <v>1</v>
+      </c>
+      <c r="G101" s="3">
+        <v>14.55039495657187</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0.15278565398844371</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>47</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F102" s="2">
+        <v>2</v>
+      </c>
+      <c r="G102" s="3">
+        <v>14.716923986485151</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0.16534818747920321</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>47</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F103" s="2">
+        <v>2</v>
+      </c>
+      <c r="G103" s="3">
+        <v>14.896773031134479</v>
+      </c>
+      <c r="H103" s="3">
+        <v>0.18750194781482851</v>
+      </c>
+      <c r="I103" s="3">
+        <v>0</v>
+      </c>
+      <c r="J103" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>47</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F104" s="2">
+        <v>2</v>
+      </c>
+      <c r="G104" s="3">
+        <v>14.55039495657187</v>
+      </c>
+      <c r="H104" s="3">
+        <v>0.15278565398844371</v>
+      </c>
+      <c r="I104" s="3">
+        <v>0</v>
+      </c>
+      <c r="J104" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
         <v>48</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F93" s="3">
+      <c r="B105" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F105" s="2">
+        <v>2</v>
+      </c>
+      <c r="G105" s="3">
         <v>12.65408035800184</v>
       </c>
-      <c r="G93" s="3">
-        <v>1.539450526251043</v>
-      </c>
-      <c r="H93" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8">
-      <c r="A94" s="1">
+      <c r="H105" s="3">
+        <v>1.5394505262510429</v>
+      </c>
+      <c r="I105" s="3">
+        <v>0</v>
+      </c>
+      <c r="J105" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
         <v>48</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B106" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F94" s="3">
-        <v>13.02541682896731</v>
-      </c>
-      <c r="G94" s="3">
-        <v>1.014068726355177</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="C106" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F106" s="2">
+        <v>2</v>
+      </c>
+      <c r="G106" s="3">
+        <v>13.025416828967311</v>
+      </c>
+      <c r="H106" s="3">
+        <v>1.0140687263551771</v>
+      </c>
+      <c r="I106" s="3">
         <v>0.9149194700052542</v>
       </c>
-    </row>
-    <row r="95" spans="1:8">
-      <c r="A95" s="1">
+      <c r="J106" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
         <v>49</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F95" s="3">
-        <v>12.765575893499</v>
-      </c>
-      <c r="G95" s="3">
+      <c r="B107" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F107" s="2">
+        <v>2</v>
+      </c>
+      <c r="G107" s="3">
+        <v>12.765575893498999</v>
+      </c>
+      <c r="H107" s="3">
         <v>1.494926220444786</v>
       </c>
-      <c r="H95" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8">
-      <c r="A96" s="1">
+      <c r="I107" s="3">
+        <v>0</v>
+      </c>
+      <c r="J107" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
         <v>49</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C96" s="2" t="s">
+      <c r="B108" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D96" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F96" s="3">
-        <v>12.89983808552675</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="D108" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F108" s="2">
+        <v>2</v>
+      </c>
+      <c r="G108" s="3">
+        <v>12.899838085526749</v>
+      </c>
+      <c r="H108" s="3">
         <v>1.291092076818368</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
-      <c r="A97" s="1">
+      <c r="I108" s="3">
+        <v>0</v>
+      </c>
+      <c r="J108" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
         <v>49</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D97" s="2" t="s">
+      <c r="B109" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D109" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E97" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F97" s="3">
+      <c r="E109" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F109" s="2">
+        <v>2</v>
+      </c>
+      <c r="G109" s="3">
         <v>12.51935568848288</v>
       </c>
-      <c r="G97" s="3">
-        <v>1.651172854389556</v>
-      </c>
-      <c r="H97" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8">
-      <c r="A98" s="1">
+      <c r="H109" s="3">
+        <v>1.6511728543895561</v>
+      </c>
+      <c r="I109" s="3">
+        <v>0</v>
+      </c>
+      <c r="J109" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
         <v>49</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E98" s="2" t="s">
+      <c r="B110" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F98" s="3">
+      <c r="F110" s="2">
+        <v>2</v>
+      </c>
+      <c r="G110" s="3">
         <v>12.66372881225416</v>
       </c>
-      <c r="G98" s="3">
+      <c r="H110" s="3">
         <v>1.579693560907643</v>
       </c>
-      <c r="H98" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8">
-      <c r="A99" s="1">
+      <c r="I110" s="3">
+        <v>0</v>
+      </c>
+      <c r="J110" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
         <v>49</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="B111" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C99" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F99" s="3">
-        <v>12.90984569288823</v>
-      </c>
-      <c r="G99" s="3">
+      <c r="C111" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F111" s="2">
+        <v>2</v>
+      </c>
+      <c r="G111" s="3">
+        <v>12.909845692888229</v>
+      </c>
+      <c r="H111" s="3">
         <v>1.273453467591432</v>
       </c>
-      <c r="H99" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8">
-      <c r="A100" s="1">
+      <c r="I111" s="3">
+        <v>0</v>
+      </c>
+      <c r="J111" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
         <v>49</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B112" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C112" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D100" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F100" s="3">
-        <v>12.89983808552675</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="D112" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F112" s="2">
+        <v>2</v>
+      </c>
+      <c r="G112" s="3">
+        <v>12.899838085526749</v>
+      </c>
+      <c r="H112" s="3">
         <v>1.291092076818368</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8">
-      <c r="A101" s="1">
+      <c r="I112" s="3">
+        <v>0</v>
+      </c>
+      <c r="J112" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
         <v>49</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="B113" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C101" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D101" s="2" t="s">
+      <c r="C113" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D113" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E101" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="E113" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F113" s="2">
+        <v>2</v>
+      </c>
+      <c r="G113" s="3">
         <v>12.51935568848288</v>
       </c>
-      <c r="G101" s="3">
-        <v>1.651172854389556</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8">
-      <c r="A102" s="1">
+      <c r="H113" s="3">
+        <v>1.6511728543895561</v>
+      </c>
+      <c r="I113" s="3">
+        <v>0</v>
+      </c>
+      <c r="J113" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
         <v>49</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E102" s="2" t="s">
+      <c r="B114" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E114" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F102" s="3">
+      <c r="F114" s="2">
+        <v>2</v>
+      </c>
+      <c r="G114" s="3">
         <v>12.66372881225416</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H114" s="3">
         <v>1.579693560907643</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8">
-      <c r="A103" s="1">
+      <c r="I114" s="3">
+        <v>0</v>
+      </c>
+      <c r="J114" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
         <v>49</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="B115" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F103" s="3">
+      <c r="C115" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F115" s="2">
+        <v>2</v>
+      </c>
+      <c r="G115" s="3">
         <v>13.27146932300206</v>
       </c>
-      <c r="G103" s="3">
-        <v>1.145301983645047</v>
-      </c>
-      <c r="H103" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8">
-      <c r="A104" s="1">
+      <c r="H115" s="3">
+        <v>1.1453019836450471</v>
+      </c>
+      <c r="I115" s="3">
+        <v>0</v>
+      </c>
+      <c r="J115" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
         <v>49</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="B116" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C116" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D104" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F104" s="3">
-        <v>12.89983808552675</v>
-      </c>
-      <c r="G104" s="3">
+      <c r="D116" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F116" s="2">
+        <v>2</v>
+      </c>
+      <c r="G116" s="3">
+        <v>12.899838085526749</v>
+      </c>
+      <c r="H116" s="3">
         <v>1.291092076818368</v>
       </c>
-      <c r="H104" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8">
-      <c r="A105" s="1">
+      <c r="I116" s="3">
+        <v>0</v>
+      </c>
+      <c r="J116" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
         <v>49</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="B117" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D105" s="2" t="s">
+      <c r="C117" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D117" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E105" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F105" s="3">
+      <c r="E117" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F117" s="2">
+        <v>2</v>
+      </c>
+      <c r="G117" s="3">
         <v>13.65645748628984</v>
       </c>
-      <c r="G105" s="3">
-        <v>1.010100057792758</v>
-      </c>
-      <c r="H105" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8">
-      <c r="A106" s="1">
+      <c r="H117" s="3">
+        <v>1.0101000577927579</v>
+      </c>
+      <c r="I117" s="3">
+        <v>0</v>
+      </c>
+      <c r="J117" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
         <v>49</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="B118" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C106" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E106" s="2" t="s">
+      <c r="C118" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E118" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F106" s="3">
-        <v>13.93218144775829</v>
-      </c>
-      <c r="G106" s="3">
-        <v>1.022881033927017</v>
-      </c>
-      <c r="H106" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8">
-      <c r="A107" s="1">
+      <c r="F118" s="2">
+        <v>2</v>
+      </c>
+      <c r="G118" s="3">
+        <v>13.932181447758291</v>
+      </c>
+      <c r="H118" s="3">
+        <v>1.0228810339270169</v>
+      </c>
+      <c r="I118" s="3">
+        <v>0</v>
+      </c>
+      <c r="J118" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
         <v>50</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F107" s="3">
-        <v>13.72687041003588</v>
-      </c>
-      <c r="G107" s="3">
-        <v>0.9623288930780104</v>
-      </c>
-      <c r="H107" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8">
-      <c r="A108" s="1">
+      <c r="B119" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F119" s="2">
+        <v>2</v>
+      </c>
+      <c r="G119" s="3">
+        <v>13.726870410035881</v>
+      </c>
+      <c r="H119" s="3">
+        <v>0.96232889307801039</v>
+      </c>
+      <c r="I119" s="3">
+        <v>0</v>
+      </c>
+      <c r="J119" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
         <v>50</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E108" s="2" t="s">
+      <c r="B120" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E120" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F108" s="3">
-        <v>8</v>
-      </c>
-      <c r="G108" s="3">
-        <v>0</v>
-      </c>
-      <c r="H108" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8">
-      <c r="A109" s="1">
+      <c r="F120" s="2">
+        <v>2</v>
+      </c>
+      <c r="G120" s="3">
+        <v>8</v>
+      </c>
+      <c r="H120" s="3">
+        <v>0</v>
+      </c>
+      <c r="I120" s="3">
+        <v>0</v>
+      </c>
+      <c r="J120" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
         <v>50</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="B121" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C109" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F109" s="3">
+      <c r="C121" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F121" s="2">
+        <v>2</v>
+      </c>
+      <c r="G121" s="3">
         <v>12.87758115026992</v>
       </c>
-      <c r="G109" s="3">
-        <v>1.493937824132873</v>
-      </c>
-      <c r="H109" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8">
-      <c r="A110" s="1">
+      <c r="H121" s="3">
+        <v>1.4939378241328729</v>
+      </c>
+      <c r="I121" s="3">
+        <v>0</v>
+      </c>
+      <c r="J121" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
         <v>50</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B122" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C122" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D110" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F110" s="3">
+      <c r="D122" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F122" s="2">
+        <v>2</v>
+      </c>
+      <c r="G122" s="3">
         <v>10</v>
       </c>
-      <c r="G110" s="3">
-        <v>0</v>
-      </c>
-      <c r="H110" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8">
-      <c r="A111" s="1">
+      <c r="H122" s="3">
+        <v>0</v>
+      </c>
+      <c r="I122" s="3">
+        <v>0</v>
+      </c>
+      <c r="J122" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
         <v>50</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="B123" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C111" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F111" s="3">
+      <c r="C123" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F123" s="2">
+        <v>2</v>
+      </c>
+      <c r="G123" s="3">
         <v>10.49915630837828</v>
       </c>
-      <c r="G111" s="3">
-        <v>0.1199538833472338</v>
-      </c>
-      <c r="H111" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8">
-      <c r="A112" s="1">
+      <c r="H123" s="3">
+        <v>0.11995388334723379</v>
+      </c>
+      <c r="I123" s="3">
+        <v>0</v>
+      </c>
+      <c r="J123" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
         <v>50</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B124" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D112" s="2" t="s">
+      <c r="C124" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D124" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E112" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F112" s="3">
-        <v>8</v>
-      </c>
-      <c r="G112" s="3">
-        <v>0</v>
-      </c>
-      <c r="H112" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8">
-      <c r="A113" s="1">
+      <c r="E124" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F124" s="2">
+        <v>2</v>
+      </c>
+      <c r="G124" s="3">
+        <v>8</v>
+      </c>
+      <c r="H124" s="3">
+        <v>0</v>
+      </c>
+      <c r="I124" s="3">
+        <v>0</v>
+      </c>
+      <c r="J124" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
         <v>51</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F113" s="3">
-        <v>14.35247433079926</v>
-      </c>
-      <c r="G113" s="3">
-        <v>0.6414093893034761</v>
-      </c>
-      <c r="H113" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8">
-      <c r="A114" s="1">
+      <c r="B125" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F125" s="2">
+        <v>2</v>
+      </c>
+      <c r="G125" s="3">
+        <v>14.352474330799261</v>
+      </c>
+      <c r="H125" s="3">
+        <v>0.64140938930347613</v>
+      </c>
+      <c r="I125" s="3">
+        <v>0</v>
+      </c>
+      <c r="J125" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
         <v>52</v>
       </c>
-      <c r="B114" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F114" s="3">
-        <v>11.78235951138486</v>
-      </c>
-      <c r="G114" s="3">
-        <v>2.033213061043078</v>
-      </c>
-      <c r="H114" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8">
-      <c r="A115" s="1">
+      <c r="B126" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F126" s="2">
+        <v>1</v>
+      </c>
+      <c r="G126" s="3">
+        <v>11.782359511384859</v>
+      </c>
+      <c r="H126" s="3">
+        <v>2.0332130610430781</v>
+      </c>
+      <c r="I126" s="3">
+        <v>0</v>
+      </c>
+      <c r="J126" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
         <v>53</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F115" s="3">
+      <c r="B127" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F127" s="2">
+        <v>2</v>
+      </c>
+      <c r="G127" s="3">
         <v>13.99147236529058</v>
       </c>
-      <c r="G115" s="3">
-        <v>0.9396807920046171</v>
-      </c>
-      <c r="H115" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8">
-      <c r="A116" s="1">
+      <c r="H127" s="3">
+        <v>0.93968079200461707</v>
+      </c>
+      <c r="I127" s="3">
+        <v>0</v>
+      </c>
+      <c r="J127" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
         <v>54</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F116" s="3">
+      <c r="B128" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F128" s="2">
+        <v>1</v>
+      </c>
+      <c r="G128" s="3">
         <v>12.78825538649768</v>
       </c>
-      <c r="G116" s="3">
+      <c r="H128" s="3">
         <v>1.526789143739075</v>
       </c>
-      <c r="H116" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8">
-      <c r="A117" s="1">
+      <c r="I128" s="3">
+        <v>0</v>
+      </c>
+      <c r="J128" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
         <v>55</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F117" s="3">
+      <c r="B129" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F129" s="2">
+        <v>2</v>
+      </c>
+      <c r="G129" s="3">
         <v>12.78312066463663</v>
       </c>
-      <c r="G117" s="3">
+      <c r="H129" s="3">
         <v>1.491896177113307</v>
       </c>
-      <c r="H117" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8">
-      <c r="A118" s="1">
+      <c r="I129" s="3">
+        <v>0</v>
+      </c>
+      <c r="J129" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
         <v>55</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C118" s="2" t="s">
+      <c r="B130" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C130" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D118" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F118" s="3">
-        <v>12.91111404415092</v>
-      </c>
-      <c r="G118" s="3">
+      <c r="D130" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F130" s="2">
+        <v>2</v>
+      </c>
+      <c r="G130" s="3">
+        <v>12.911114044150921</v>
+      </c>
+      <c r="H130" s="3">
         <v>1.428235862000192</v>
       </c>
-      <c r="H118" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8">
-      <c r="A119" s="1">
+      <c r="I130" s="3">
+        <v>0</v>
+      </c>
+      <c r="J130" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
         <v>55</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="B131" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C119" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F119" s="3">
+      <c r="C131" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F131" s="2">
+        <v>2</v>
+      </c>
+      <c r="G131" s="3">
         <v>12.92222293461186</v>
       </c>
-      <c r="G119" s="3">
-        <v>1.270622127841042</v>
-      </c>
-      <c r="H119" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8">
-      <c r="A120" s="1">
+      <c r="H131" s="3">
+        <v>1.2706221278410419</v>
+      </c>
+      <c r="I131" s="3">
+        <v>0</v>
+      </c>
+      <c r="J131" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
         <v>55</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="B132" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C120" s="2" t="s">
+      <c r="C132" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D120" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F120" s="3">
-        <v>12.91111404415092</v>
-      </c>
-      <c r="G120" s="3">
+      <c r="D132" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F132" s="2">
+        <v>2</v>
+      </c>
+      <c r="G132" s="3">
+        <v>12.911114044150921</v>
+      </c>
+      <c r="H132" s="3">
         <v>1.428235862000192</v>
       </c>
-      <c r="H120" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8">
-      <c r="A121" s="1">
+      <c r="I132" s="3">
+        <v>0</v>
+      </c>
+      <c r="J132" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
         <v>55</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="B133" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C121" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F121" s="3">
+      <c r="C133" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F133" s="2">
+        <v>2</v>
+      </c>
+      <c r="G133" s="3">
         <v>13.31655710958051</v>
       </c>
-      <c r="G121" s="3">
-        <v>1.136814391737674</v>
-      </c>
-      <c r="H121" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8">
-      <c r="A122" s="1">
+      <c r="H133" s="3">
+        <v>1.1368143917376741</v>
+      </c>
+      <c r="I133" s="3">
+        <v>0</v>
+      </c>
+      <c r="J133" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
         <v>55</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B134" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C122" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F122" s="3">
-        <v>12.91111404415092</v>
-      </c>
-      <c r="G122" s="3">
+      <c r="C134" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F134" s="2">
+        <v>2</v>
+      </c>
+      <c r="G134" s="3">
+        <v>12.911114044150921</v>
+      </c>
+      <c r="H134" s="3">
         <v>1.428235862000192</v>
       </c>
-      <c r="H122" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8">
-      <c r="A123" s="1">
+      <c r="I134" s="3">
+        <v>0</v>
+      </c>
+      <c r="J134" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
         <v>56</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F123" s="3">
+      <c r="B135" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F135" s="2">
+        <v>1</v>
+      </c>
+      <c r="G135" s="3">
         <v>12.84406077189395</v>
       </c>
-      <c r="G123" s="3">
+      <c r="H135" s="3">
         <v>1.511330448649495</v>
       </c>
-      <c r="H123" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8">
-      <c r="A124" s="1">
+      <c r="I135" s="3">
+        <v>0</v>
+      </c>
+      <c r="J135" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
         <v>56</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B136" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C124" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F124" s="3">
-        <v>12.95353986568809</v>
-      </c>
-      <c r="G124" s="3">
+      <c r="C136" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F136" s="2">
+        <v>1</v>
+      </c>
+      <c r="G136" s="3">
+        <v>12.953539865688089</v>
+      </c>
+      <c r="H136" s="3">
         <v>1.422083436886725</v>
       </c>
-      <c r="H124" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8">
-      <c r="A125" s="1">
+      <c r="I136" s="3">
+        <v>0</v>
+      </c>
+      <c r="J136" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
         <v>56</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="B137" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C125" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F125" s="3">
-        <v>13.06279486628008</v>
-      </c>
-      <c r="G125" s="3">
-        <v>1.333019105195146</v>
-      </c>
-      <c r="H125" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8">
-      <c r="A126" s="1">
+      <c r="C137" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F137" s="2">
+        <v>1</v>
+      </c>
+      <c r="G137" s="3">
+        <v>13.062794866280081</v>
+      </c>
+      <c r="H137" s="3">
+        <v>1.3330191051951461</v>
+      </c>
+      <c r="I137" s="3">
+        <v>0</v>
+      </c>
+      <c r="J137" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
         <v>57</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F126" s="3">
-        <v>10.1070572630632</v>
-      </c>
-      <c r="G126" s="3">
-        <v>0.08127279657798771</v>
-      </c>
-      <c r="H126" s="3">
-        <v>0</v>
+      <c r="B138" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F138" s="2">
+        <v>2</v>
+      </c>
+      <c r="G138" s="3">
+        <v>10.107057263063201</v>
+      </c>
+      <c r="H138" s="3">
+        <v>8.1272796577987708E-2</v>
+      </c>
+      <c r="I138" s="3">
+        <v>0</v>
+      </c>
+      <c r="J138" s="4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/UnifacDortmund/Experimental_Data/data/profile_coeffs.xlsx
+++ b/UnifacDortmund/Experimental_Data/data/profile_coeffs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Juan\proyectos_personales\Maestría\Materias\Tesis\oleosim\UnifacDortmund\Experimental_Data\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8A0F0B-2D4C-4148-87CB-59A8A4787BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030E3B24-7CCE-4E96-AB03-4BB4BCDD9221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -156,7 +156,7 @@
       <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
@@ -165,7 +165,7 @@
       <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="#,##0;[Red]\-#,##0"/>
@@ -192,10 +192,10 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="MAG/DAG Profile?"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Additional FAME Profile?"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Acid mix Profile?"/>
-    <tableColumn id="9" xr3:uid="{9F057E55-9F2C-4F9F-BF85-42F7D5BDEAEE}" name="Type Alcohol" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="m" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="n" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="p" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{9F057E55-9F2C-4F9F-BF85-42F7D5BDEAEE}" name="Type Alcohol" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="m" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="n" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="p" dataDxfId="1"/>
     <tableColumn id="10" xr3:uid="{A79D96DD-C468-4203-886B-C43662C6B702}" name="b" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -491,6 +491,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J138"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">

--- a/UnifacDortmund/Experimental_Data/data/profile_coeffs.xlsx
+++ b/UnifacDortmund/Experimental_Data/data/profile_coeffs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Juan\proyectos_personales\Maestría\Materias\Tesis\oleosim\UnifacDortmund\Experimental_Data\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030E3B24-7CCE-4E96-AB03-4BB4BCDD9221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0743DBFB-3820-46F1-9EA2-5917A3E0A17F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4760,7 +4760,7 @@
         <v>10</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>12</v>
